--- a/nord-kivu/sortie/zs/Beni/Tableaux_ZS_Beni_20261014.xlsx
+++ b/nord-kivu/sortie/zs/Beni/Tableaux_ZS_Beni_20261014.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rapport de suivi'!$A$1:$Q$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bulletin des aires'!$A$1:$P$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Suivi quotidien (ZS)'!$A$1:$F$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cas'!$A$1:$S$482</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SBC 7 jours'!$A$1:$R$27</definedName>
@@ -2051,10 +2051,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -2157,223 +2157,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Benengule</t>
+          <t>31 Bde</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>309</v>
-      </c>
-      <c r="J2" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
-      </c>
-      <c r="M2" t="n">
-        <v>77</v>
-      </c>
-      <c r="N2" t="n">
-        <v>93</v>
-      </c>
-      <c r="O2" t="n">
-        <v>100</v>
-      </c>
-      <c r="P2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boikene</t>
+          <t>Balayi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>341</v>
-      </c>
-      <c r="J3" t="n">
-        <v>69.5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
-      </c>
-      <c r="M3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N3" t="n">
-        <v>29</v>
-      </c>
-      <c r="O3" t="n">
-        <v>94</v>
-      </c>
-      <c r="P3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bundji</t>
+          <t>Bel Air</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>344</v>
-      </c>
-      <c r="J4" t="n">
-        <v>64.8</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>113</v>
-      </c>
-      <c r="M4" t="n">
-        <v>81</v>
-      </c>
-      <c r="N4" t="n">
-        <v>53</v>
-      </c>
-      <c r="O4" t="n">
-        <v>100</v>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Butanuka</t>
+          <t>Bel Aire</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>89.5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N5" t="n">
-        <v>65</v>
-      </c>
-      <c r="O5" t="n">
-        <v>64</v>
-      </c>
-      <c r="P5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Butembo</t>
+          <t>Benengole</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2403,7 +2307,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Butsili</t>
+          <t>Benengule</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2412,214 +2316,142 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>17.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I7" t="n">
-        <v>916</v>
+        <v>309</v>
       </c>
       <c r="J7" t="n">
-        <v>76.5</v>
+        <v>84.8</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="O7" t="n">
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kanzulinzuli</t>
+          <t>Bengengule</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>474</v>
-      </c>
-      <c r="J8" t="n">
-        <v>75.3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>105</v>
-      </c>
-      <c r="M8" t="n">
-        <v>39</v>
-      </c>
-      <c r="N8" t="n">
-        <v>45</v>
-      </c>
-      <c r="O8" t="n">
-        <v>92</v>
-      </c>
-      <c r="P8" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kasabinyole</t>
+          <t>Beni</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>155</v>
-      </c>
-      <c r="J9" t="n">
-        <v>68.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>86</v>
-      </c>
-      <c r="N9" t="n">
-        <v>47</v>
-      </c>
-      <c r="O9" t="n">
-        <v>100</v>
-      </c>
-      <c r="P9" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kasanga</t>
+          <t>Biautu Kilokwa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>492</v>
-      </c>
-      <c r="J10" t="n">
-        <v>91.5</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
-      </c>
-      <c r="M10" t="n">
-        <v>80</v>
-      </c>
-      <c r="N10" t="n">
-        <v>63</v>
-      </c>
-      <c r="O10" t="n">
-        <v>100</v>
-      </c>
-      <c r="P10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kuka</t>
+          <t>Boikene</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2628,106 +2460,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>159</v>
+        <v>341</v>
       </c>
       <c r="J11" t="n">
-        <v>93.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="O11" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mabakanga</t>
+          <t>Budji</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>128</v>
-      </c>
-      <c r="J12" t="n">
-        <v>78.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M12" t="n">
-        <v>92</v>
-      </c>
-      <c r="N12" t="n">
-        <v>46</v>
-      </c>
-      <c r="O12" t="n">
-        <v>100</v>
-      </c>
-      <c r="P12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mabolio</t>
+          <t>Bundji</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2736,40 +2544,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>5.6</v>
+        <v>24.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="J13" t="n">
-        <v>57.6</v>
+        <v>64.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="M13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="N13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="O13" t="n">
         <v>100</v>
@@ -2781,61 +2589,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Madrandele</t>
+          <t>Bunengule</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>278</v>
-      </c>
-      <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
-      </c>
-      <c r="M14" t="n">
-        <v>100</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>100</v>
-      </c>
-      <c r="P14" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Malepe</t>
+          <t>Butanuka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2847,40 +2631,40 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
       <c r="H15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>62.1</v>
+        <v>89.5</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="P15" t="n">
         <v>100</v>
@@ -2889,61 +2673,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mangothe</t>
+          <t>Butembo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1085</v>
-      </c>
-      <c r="J16" t="n">
-        <v>71.2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>220</v>
-      </c>
-      <c r="M16" t="n">
-        <v>91</v>
-      </c>
-      <c r="N16" t="n">
-        <v>84</v>
-      </c>
-      <c r="O16" t="n">
-        <v>100</v>
-      </c>
-      <c r="P16" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mukulya</t>
+          <t>Butsili</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2952,106 +2712,82 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>5.9</v>
+        <v>17.1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I17" t="n">
-        <v>273</v>
+        <v>916</v>
       </c>
       <c r="J17" t="n">
-        <v>86.8</v>
+        <v>76.5</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="M17" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="N17" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="O17" t="n">
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ndindi</t>
+          <t>Butunuka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>55</v>
-      </c>
-      <c r="J18" t="n">
-        <v>61.8</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
-      </c>
-      <c r="M18" t="n">
-        <v>100</v>
-      </c>
-      <c r="N18" t="n">
-        <v>99</v>
-      </c>
-      <c r="O18" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ngadi</t>
+          <t>Cite Belge</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3068,155 +2804,89 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
-        <v>86</v>
-      </c>
-      <c r="J19" t="n">
-        <v>82.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
-      </c>
-      <c r="M19" t="n">
-        <v>100</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>100</v>
-      </c>
-      <c r="P19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ngilinga</t>
+          <t>Cite Belle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>164</v>
-      </c>
-      <c r="J20" t="n">
-        <v>81.7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>28</v>
-      </c>
-      <c r="M20" t="n">
-        <v>99</v>
-      </c>
-      <c r="N20" t="n">
-        <v>69</v>
-      </c>
-      <c r="O20" t="n">
-        <v>100</v>
-      </c>
-      <c r="P20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ngongolio</t>
+          <t>Cs Kanzulinzuli</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>757</v>
-      </c>
-      <c r="J21" t="n">
-        <v>65.7</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>251</v>
-      </c>
-      <c r="M21" t="n">
-        <v>57</v>
-      </c>
-      <c r="N21" t="n">
-        <v>27</v>
-      </c>
-      <c r="O21" t="n">
-        <v>90</v>
-      </c>
-      <c r="P21" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nzuma</t>
+          <t>Cs Kivetya</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verte</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -3224,149 +2894,80 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>49</v>
-      </c>
       <c r="I22" t="n">
-        <v>79</v>
-      </c>
-      <c r="J22" t="n">
-        <v>97.5</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>74</v>
-      </c>
-      <c r="N22" t="n">
-        <v>69</v>
-      </c>
-      <c r="O22" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paida</t>
+          <t>Cs Ndindi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>86</v>
-      </c>
-      <c r="J23" t="n">
-        <v>72.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>23</v>
-      </c>
-      <c r="M23" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" t="n">
-        <v>63</v>
-      </c>
-      <c r="O23" t="n">
-        <v>100</v>
-      </c>
-      <c r="P23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rwangoma</t>
+          <t>Cs Nzuma</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10</v>
-      </c>
-      <c r="H24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>52</v>
-      </c>
-      <c r="J24" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
-      </c>
-      <c r="M24" t="n">
-        <v>95</v>
-      </c>
-      <c r="N24" t="n">
-        <v>51</v>
-      </c>
-      <c r="O24" t="n">
-        <v>100</v>
-      </c>
-      <c r="P24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sayo</t>
+          <t>Eringeti</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3383,198 +2984,3477 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" t="n">
-        <v>25</v>
-      </c>
-      <c r="J25" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>86</v>
-      </c>
-      <c r="N25" t="n">
-        <v>100</v>
-      </c>
-      <c r="O25" t="n">
-        <v>90</v>
-      </c>
-      <c r="P25" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supa</t>
+          <t>Hgr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>11</v>
-      </c>
-      <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>100</v>
-      </c>
-      <c r="N26" t="n">
-        <v>55</v>
-      </c>
-      <c r="O26" t="n">
-        <v>100</v>
-      </c>
-      <c r="P26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tamende</t>
+          <t>Hgr Beni</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rouge</t>
+          <t>Non touchée</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>204</v>
-      </c>
-      <c r="J27" t="n">
-        <v>71.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
-      </c>
-      <c r="M27" t="n">
-        <v>100</v>
-      </c>
-      <c r="N27" t="n">
-        <v>57</v>
-      </c>
-      <c r="O27" t="n">
-        <v>100</v>
-      </c>
-      <c r="P27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Hgr Oicha</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kabasha</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kalimango</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kalinda</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kalongo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kalunguta</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kamango</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kangaembi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kangaimbi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kangbayi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kangwai</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kangwayi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kanzuli</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kanzulinzuli</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>42</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13</v>
+      </c>
+      <c r="I41" t="n">
+        <v>474</v>
+      </c>
+      <c r="J41" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>12</v>
+      </c>
+      <c r="L41" t="n">
+        <v>105</v>
+      </c>
+      <c r="M41" t="n">
+        <v>39</v>
+      </c>
+      <c r="N41" t="n">
+        <v>45</v>
+      </c>
+      <c r="O41" t="n">
+        <v>92</v>
+      </c>
+      <c r="P41" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Kanzunzuli</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kasabi</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Kasabinyole</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>17</v>
+      </c>
+      <c r="I44" t="n">
+        <v>155</v>
+      </c>
+      <c r="J44" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>48</v>
+      </c>
+      <c r="M44" t="n">
+        <v>86</v>
+      </c>
+      <c r="N44" t="n">
+        <v>47</v>
+      </c>
+      <c r="O44" t="n">
+        <v>100</v>
+      </c>
+      <c r="P44" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kasanga</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>13</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>17</v>
+      </c>
+      <c r="I45" t="n">
+        <v>492</v>
+      </c>
+      <c r="J45" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>30</v>
+      </c>
+      <c r="M45" t="n">
+        <v>80</v>
+      </c>
+      <c r="N45" t="n">
+        <v>63</v>
+      </c>
+      <c r="O45" t="n">
+        <v>100</v>
+      </c>
+      <c r="P45" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kasanga Tuha</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kasika</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kasindi</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Kididiwe</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kilikoma</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kilokwa</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kuka</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>159</v>
+      </c>
+      <c r="J52" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>100</v>
+      </c>
+      <c r="N52" t="n">
+        <v>64</v>
+      </c>
+      <c r="O52" t="n">
+        <v>100</v>
+      </c>
+      <c r="P52" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Kyatsaba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Labreche</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mabakanga</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>128</v>
+      </c>
+      <c r="J55" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>24</v>
+      </c>
+      <c r="M55" t="n">
+        <v>92</v>
+      </c>
+      <c r="N55" t="n">
+        <v>46</v>
+      </c>
+      <c r="O55" t="n">
+        <v>100</v>
+      </c>
+      <c r="P55" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Mabakou</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mabalako</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mabanga</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mabatali</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mabo</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mabolia</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mabolio</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>60</v>
+      </c>
+      <c r="I62" t="n">
+        <v>139</v>
+      </c>
+      <c r="J62" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>50</v>
+      </c>
+      <c r="M62" t="n">
+        <v>88</v>
+      </c>
+      <c r="N62" t="n">
+        <v>36</v>
+      </c>
+      <c r="O62" t="n">
+        <v>100</v>
+      </c>
+      <c r="P62" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mabolyo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Macambanye</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Macampagne</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Madrandele</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>14</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>278</v>
+      </c>
+      <c r="J66" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" t="n">
+        <v>40</v>
+      </c>
+      <c r="M66" t="n">
+        <v>100</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>100</v>
+      </c>
+      <c r="P66" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Magambanye</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Malepe</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>25</v>
+      </c>
+      <c r="I68" t="n">
+        <v>153</v>
+      </c>
+      <c r="J68" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>55</v>
+      </c>
+      <c r="M68" t="n">
+        <v>24</v>
+      </c>
+      <c r="N68" t="n">
+        <v>100</v>
+      </c>
+      <c r="O68" t="n">
+        <v>100</v>
+      </c>
+      <c r="P68" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Malese</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Mambakanga</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mambanga</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Mambango</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Mandrande</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mandrandele</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Manghote</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Mangina</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Mangombi</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Mangothe</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>70</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7</v>
+      </c>
+      <c r="E78" t="n">
+        <v>21</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>43</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1085</v>
+      </c>
+      <c r="J78" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>59</v>
+      </c>
+      <c r="L78" t="n">
+        <v>220</v>
+      </c>
+      <c r="M78" t="n">
+        <v>91</v>
+      </c>
+      <c r="N78" t="n">
+        <v>84</v>
+      </c>
+      <c r="O78" t="n">
+        <v>100</v>
+      </c>
+      <c r="P78" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mapele</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mapera</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Maseka</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Masiani</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Matembo</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Mathonge</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Matonge</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Mavivi</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mayuwano</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mikulia</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mukulya</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>273</v>
+      </c>
+      <c r="J89" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="K89" t="n">
+        <v>14</v>
+      </c>
+      <c r="L89" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" t="n">
+        <v>53</v>
+      </c>
+      <c r="N89" t="n">
+        <v>100</v>
+      </c>
+      <c r="O89" t="n">
+        <v>100</v>
+      </c>
+      <c r="P89" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Muloku</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Musenze</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mutube</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mutwanga</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Muzambai</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ndindi</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>18</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>17</v>
+      </c>
+      <c r="I95" t="n">
+        <v>55</v>
+      </c>
+      <c r="J95" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>6</v>
+      </c>
+      <c r="L95" t="n">
+        <v>15</v>
+      </c>
+      <c r="M95" t="n">
+        <v>100</v>
+      </c>
+      <c r="N95" t="n">
+        <v>99</v>
+      </c>
+      <c r="O95" t="n">
+        <v>98</v>
+      </c>
+      <c r="P95" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ngadi</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>86</v>
+      </c>
+      <c r="J96" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" t="n">
+        <v>100</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>100</v>
+      </c>
+      <c r="P96" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ngalinga</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ngilinga</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>25</v>
+      </c>
+      <c r="I98" t="n">
+        <v>164</v>
+      </c>
+      <c r="J98" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>28</v>
+      </c>
+      <c r="M98" t="n">
+        <v>99</v>
+      </c>
+      <c r="N98" t="n">
+        <v>69</v>
+      </c>
+      <c r="O98" t="n">
+        <v>100</v>
+      </c>
+      <c r="P98" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ngongolio</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>56</v>
+      </c>
+      <c r="D99" t="n">
+        <v>9</v>
+      </c>
+      <c r="E99" t="n">
+        <v>26</v>
+      </c>
+      <c r="F99" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>35</v>
+      </c>
+      <c r="I99" t="n">
+        <v>757</v>
+      </c>
+      <c r="J99" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="K99" t="n">
+        <v>6</v>
+      </c>
+      <c r="L99" t="n">
+        <v>251</v>
+      </c>
+      <c r="M99" t="n">
+        <v>57</v>
+      </c>
+      <c r="N99" t="n">
+        <v>27</v>
+      </c>
+      <c r="O99" t="n">
+        <v>90</v>
+      </c>
+      <c r="P99" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Niyaniya</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ntoni</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Nzuma</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Verte</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>49</v>
+      </c>
+      <c r="I102" t="n">
+        <v>79</v>
+      </c>
+      <c r="J102" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>74</v>
+      </c>
+      <c r="N102" t="n">
+        <v>69</v>
+      </c>
+      <c r="O102" t="n">
+        <v>100</v>
+      </c>
+      <c r="P102" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Paida</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4</v>
+      </c>
+      <c r="H103" t="n">
+        <v>20</v>
+      </c>
+      <c r="I103" t="n">
+        <v>86</v>
+      </c>
+      <c r="J103" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>23</v>
+      </c>
+      <c r="M103" t="n">
+        <v>100</v>
+      </c>
+      <c r="N103" t="n">
+        <v>63</v>
+      </c>
+      <c r="O103" t="n">
+        <v>100</v>
+      </c>
+      <c r="P103" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Paida Kitahomba</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Paiida</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Pasisi</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Residentiel</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Rurangoma</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Rwangoma</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>10</v>
+      </c>
+      <c r="H109" t="n">
+        <v>33</v>
+      </c>
+      <c r="I109" t="n">
+        <v>52</v>
+      </c>
+      <c r="J109" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>35</v>
+      </c>
+      <c r="M109" t="n">
+        <v>95</v>
+      </c>
+      <c r="N109" t="n">
+        <v>51</v>
+      </c>
+      <c r="O109" t="n">
+        <v>100</v>
+      </c>
+      <c r="P109" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Rwenzori</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sayo</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>25</v>
+      </c>
+      <c r="J111" t="n">
+        <v>76</v>
+      </c>
+      <c r="K111" t="n">
+        <v>6</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>86</v>
+      </c>
+      <c r="N111" t="n">
+        <v>100</v>
+      </c>
+      <c r="O111" t="n">
+        <v>90</v>
+      </c>
+      <c r="P111" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Siriwayo</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sose</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Supa</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>11</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>8</v>
+      </c>
+      <c r="J114" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>100</v>
+      </c>
+      <c r="N114" t="n">
+        <v>55</v>
+      </c>
+      <c r="O114" t="n">
+        <v>100</v>
+      </c>
+      <c r="P114" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tamende</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rouge</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>15</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>204</v>
+      </c>
+      <c r="J115" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>45</v>
+      </c>
+      <c r="M115" t="n">
+        <v>100</v>
+      </c>
+      <c r="N115" t="n">
+        <v>57</v>
+      </c>
+      <c r="O115" t="n">
+        <v>100</v>
+      </c>
+      <c r="P115" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tamene</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tamnde</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tenambo</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Tuungane</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Rouge</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C119" t="n">
         <v>17</v>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
         <v>2</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F119" t="n">
         <v>10</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G119" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
         <v>81</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J119" t="n">
         <v>44.4</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
         <v>44</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M119" t="n">
         <v>82</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N119" t="n">
         <v>56</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O119" t="n">
         <v>94</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P119" t="n">
         <v>100</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tuungano</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Vemba</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Vighole</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Vingazi</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Vutsili</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Non touchée</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P28"/>
+  <autoFilter ref="A1:P124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
